--- a/Team-Data/2012-13/3-12-2012-13.xlsx
+++ b/Team-Data/2012-13/3-12-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
         <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.54</v>
+        <v>0.548</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
@@ -679,25 +746,25 @@
         <v>37.4</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K2" t="n">
         <v>0.462</v>
       </c>
       <c r="L2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>23.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
         <v>13.5</v>
       </c>
       <c r="P2" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="Q2" t="n">
         <v>0.705</v>
@@ -706,46 +773,46 @@
         <v>9.4</v>
       </c>
       <c r="S2" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T2" t="n">
         <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="V2" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
         <v>7.9</v>
       </c>
       <c r="X2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -793,22 +860,22 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
         <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
         <v>34</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.54</v>
+        <v>0.548</v>
       </c>
       <c r="H3" t="n">
         <v>49.3</v>
       </c>
       <c r="I3" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J3" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L3" t="n">
         <v>5.9</v>
       </c>
       <c r="M3" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O3" t="n">
         <v>16.2</v>
@@ -882,25 +949,25 @@
         <v>20.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.778</v>
+        <v>0.781</v>
       </c>
       <c r="R3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="S3" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="U3" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V3" t="n">
         <v>14.5</v>
       </c>
       <c r="W3" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X3" t="n">
         <v>4.3</v>
@@ -915,19 +982,19 @@
         <v>19.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.7</v>
+        <v>96</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>12</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
@@ -939,7 +1006,7 @@
         <v>17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
         <v>9</v>
@@ -954,31 +1021,31 @@
         <v>22</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -1025,61 +1092,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.585</v>
+        <v>0.578</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
         <v>79.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L4" t="n">
         <v>7.8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O4" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P4" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R4" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S4" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T4" t="n">
         <v>42.6</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1088,25 +1155,25 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z4" t="n">
         <v>18.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.2</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF4" t="n">
         <v>9</v>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,10 +1200,10 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="n">
         <v>13</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>12</v>
       </c>
       <c r="AP4" t="n">
         <v>8</v>
@@ -1148,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
         <v>14</v>
@@ -1157,7 +1224,7 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,7 +1292,7 @@
         <v>34.2</v>
       </c>
       <c r="J5" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.418</v>
@@ -1243,22 +1310,22 @@
         <v>18.9</v>
       </c>
       <c r="P5" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="R5" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S5" t="n">
         <v>29</v>
       </c>
       <c r="T5" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U5" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V5" t="n">
         <v>13.9</v>
@@ -1267,25 +1334,25 @@
         <v>7.1</v>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA5" t="n">
         <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-10</v>
+        <v>-10.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1321,13 +1388,13 @@
         <v>4</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS5" t="n">
         <v>28</v>
@@ -1351,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1482,7 +1549,7 @@
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ6" t="n">
         <v>19</v>
@@ -1518,7 +1585,7 @@
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
         <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>0.344</v>
+        <v>0.333</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1598,10 +1665,10 @@
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O7" t="n">
         <v>17.5</v>
@@ -1613,19 +1680,19 @@
         <v>0.761</v>
       </c>
       <c r="R7" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S7" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="T7" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U7" t="n">
         <v>20.6</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W7" t="n">
         <v>8</v>
@@ -1634,31 +1701,31 @@
         <v>3.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Z7" t="n">
         <v>21.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
         <v>97.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
@@ -1715,16 +1782,16 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
         <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" t="n">
         <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>0.476</v>
+        <v>0.468</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
@@ -1771,37 +1838,37 @@
         <v>38.5</v>
       </c>
       <c r="J8" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K8" t="n">
         <v>0.457</v>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M8" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="N8" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O8" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P8" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0.792</v>
       </c>
       <c r="R8" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S8" t="n">
         <v>32.9</v>
       </c>
       <c r="T8" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U8" t="n">
         <v>23</v>
@@ -1825,13 +1892,13 @@
         <v>19.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.4</v>
+        <v>101.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1846,7 +1913,7 @@
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
         <v>3</v>
@@ -1855,7 +1922,7 @@
         <v>10</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1864,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
         <v>21</v>
@@ -1876,19 +1943,19 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2043,7 +2110,7 @@
         <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
@@ -2058,7 +2125,7 @@
         <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>3</v>
@@ -2067,7 +2134,7 @@
         <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2268,7 @@
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
@@ -2216,7 +2283,7 @@
         <v>20</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>22</v>
@@ -2243,19 +2310,19 @@
         <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2450,7 @@
         <v>10</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
@@ -2395,10 +2462,10 @@
         <v>10</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2626,13 @@
         <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
         <v>14</v>
@@ -2574,7 +2641,7 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ12" t="n">
         <v>10</v>
@@ -2592,10 +2659,10 @@
         <v>6</v>
       </c>
       <c r="AO12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>17</v>
@@ -2607,10 +2674,10 @@
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2622,13 +2689,13 @@
         <v>28</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2759,7 +2826,7 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK13" t="n">
         <v>25</v>
@@ -2786,7 +2853,7 @@
         <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
@@ -2953,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="AN14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>19</v>
@@ -2965,10 +3032,10 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT14" t="n">
         <v>18</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
         <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>0.523</v>
+        <v>0.516</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K15" t="n">
         <v>0.46</v>
@@ -3060,28 +3127,28 @@
         <v>0.358</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S15" t="n">
         <v>33</v>
       </c>
       <c r="T15" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U15" t="n">
         <v>22</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
         <v>7.1</v>
@@ -3090,31 +3157,31 @@
         <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB15" t="n">
         <v>102.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AF15" t="n">
         <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3123,7 +3190,7 @@
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
         <v>8</v>
@@ -3138,7 +3205,7 @@
         <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -3150,7 +3217,7 @@
         <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
@@ -3159,7 +3226,7 @@
         <v>16</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AW15" t="n">
         <v>22</v>
@@ -3171,7 +3238,7 @@
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -3209,64 +3276,64 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.694</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J16" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O16" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P16" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.775</v>
+        <v>0.778</v>
       </c>
       <c r="R16" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S16" t="n">
         <v>29.5</v>
       </c>
       <c r="T16" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U16" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="V16" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>5.3</v>
@@ -3275,13 +3342,13 @@
         <v>5.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.8</v>
+        <v>93.7</v>
       </c>
       <c r="AC16" t="n">
         <v>4.3</v>
@@ -3290,13 +3357,13 @@
         <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="n">
         <v>20</v>
@@ -3308,7 +3375,7 @@
         <v>12</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,16 +3384,16 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR16" t="n">
         <v>1</v>
@@ -3335,10 +3402,10 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
@@ -3347,7 +3414,7 @@
         <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -3391,64 +3458,64 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.774</v>
+        <v>0.77</v>
       </c>
       <c r="H17" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I17" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J17" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.495</v>
+        <v>0.496</v>
       </c>
       <c r="L17" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M17" t="n">
         <v>21</v>
       </c>
       <c r="N17" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R17" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T17" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="U17" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V17" t="n">
         <v>13.5</v>
       </c>
       <c r="W17" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X17" t="n">
         <v>5.1</v>
@@ -3457,16 +3524,16 @@
         <v>3.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AD17" t="n">
         <v>25</v>
@@ -3514,7 +3581,7 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" t="n">
         <v>32</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.516</v>
+        <v>0.525</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3591,49 +3658,49 @@
         <v>38.1</v>
       </c>
       <c r="J18" t="n">
-        <v>86.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L18" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M18" t="n">
         <v>18.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O18" t="n">
         <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="R18" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S18" t="n">
         <v>31</v>
       </c>
       <c r="T18" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="U18" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V18" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W18" t="n">
         <v>8.5</v>
       </c>
       <c r="X18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="Y18" t="n">
         <v>4.4</v>
@@ -3645,10 +3712,10 @@
         <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
         <v>25</v>
@@ -3657,10 +3724,10 @@
         <v>17</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>14</v>
@@ -3693,7 +3760,7 @@
         <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
         <v>13</v>
@@ -3702,13 +3769,13 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV18" t="n">
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3717,7 +3784,7 @@
         <v>8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -3755,88 +3822,88 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
         <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>0.361</v>
+        <v>0.35</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J19" t="n">
         <v>81.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.433</v>
+        <v>0.431</v>
       </c>
       <c r="L19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M19" t="n">
         <v>17.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.299</v>
+        <v>0.293</v>
       </c>
       <c r="O19" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.728</v>
+        <v>0.732</v>
       </c>
       <c r="R19" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S19" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T19" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V19" t="n">
         <v>15.2</v>
       </c>
       <c r="W19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF19" t="n">
         <v>20</v>
@@ -3848,10 +3915,10 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -3875,7 +3942,7 @@
         <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
@@ -3884,19 +3951,19 @@
         <v>9</v>
       </c>
       <c r="AU19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ19" t="n">
         <v>5</v>
@@ -3905,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -3937,61 +4004,61 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J20" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L20" t="n">
         <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O20" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R20" t="n">
         <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W20" t="n">
         <v>6.3</v>
@@ -4000,31 +4067,31 @@
         <v>5.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA20" t="n">
         <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
@@ -4036,7 +4103,7 @@
         <v>25</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>17</v>
@@ -4048,13 +4115,13 @@
         <v>7</v>
       </c>
       <c r="AO20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
         <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
         <v>14</v>
@@ -4063,10 +4130,10 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU20" t="n">
         <v>22</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>23</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
@@ -4087,10 +4154,10 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC20" t="n">
         <v>22</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4245,7 +4312,7 @@
         <v>23</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4430,7 +4497,7 @@
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G23" t="n">
-        <v>0.277</v>
+        <v>0.281</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,19 +4568,19 @@
         <v>37.7</v>
       </c>
       <c r="J23" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L23" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O23" t="n">
         <v>12.3</v>
@@ -4534,13 +4601,13 @@
         <v>42.3</v>
       </c>
       <c r="U23" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X23" t="n">
         <v>4.2</v>
@@ -4549,7 +4616,7 @@
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="AA23" t="n">
         <v>16.5</v>
@@ -4558,10 +4625,10 @@
         <v>94.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,16 +4640,16 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
         <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4600,19 +4667,19 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
         <v>16</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
         <v>14</v>
@@ -4627,7 +4694,7 @@
         <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>21</v>
@@ -4791,7 +4858,7 @@
         <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>12</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4992,19 @@
         <v>-5.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
         <v>23</v>
       </c>
       <c r="AF25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG25" t="n">
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
         <v>13</v>
@@ -4979,7 +5046,7 @@
         <v>15</v>
       </c>
       <c r="AV25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW25" t="n">
         <v>15</v>
@@ -4991,7 +5058,7 @@
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E26" t="n">
         <v>29</v>
       </c>
       <c r="F26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G26" t="n">
-        <v>0.46</v>
+        <v>0.468</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J26" t="n">
         <v>82</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="N26" t="n">
         <v>0.347</v>
       </c>
       <c r="O26" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P26" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.778</v>
+        <v>0.774</v>
       </c>
       <c r="R26" t="n">
         <v>11.1</v>
@@ -5080,7 +5147,7 @@
         <v>41.4</v>
       </c>
       <c r="U26" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V26" t="n">
         <v>14.8</v>
@@ -5095,10 +5162,10 @@
         <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB26" t="n">
         <v>98</v>
@@ -5107,16 +5174,16 @@
         <v>-1.8</v>
       </c>
       <c r="AD26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE26" t="n">
         <v>18</v>
       </c>
-      <c r="AE26" t="n">
-        <v>19</v>
-      </c>
       <c r="AF26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
         <v>6</v>
@@ -5146,7 +5213,7 @@
         <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
         <v>18</v>
@@ -5155,7 +5222,7 @@
         <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
@@ -5167,10 +5234,10 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5362,7 @@
         <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG27" t="n">
         <v>26</v>
@@ -5310,7 +5377,7 @@
         <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL27" t="n">
         <v>14</v>
@@ -5343,10 +5410,10 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
@@ -5355,7 +5422,7 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA27" t="n">
         <v>14</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -5393,61 +5460,61 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E28" t="n">
         <v>49</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>0.754</v>
+        <v>0.766</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="J28" t="n">
         <v>81.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.487</v>
+        <v>0.49</v>
       </c>
       <c r="L28" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O28" t="n">
         <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
       <c r="R28" t="n">
         <v>7.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T28" t="n">
         <v>40.9</v>
       </c>
       <c r="U28" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
         <v>8.699999999999999</v>
@@ -5456,22 +5523,22 @@
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AA28" t="n">
         <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.4</v>
+        <v>104.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,13 +5550,13 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,7 +5571,7 @@
         <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP28" t="n">
         <v>19</v>
@@ -5525,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5674,10 +5741,10 @@
         <v>11</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM29" t="n">
         <v>8</v>
@@ -5701,10 +5768,10 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5713,10 +5780,10 @@
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-0.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF30" t="n">
         <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>8</v>
@@ -5856,7 +5923,7 @@
         <v>13</v>
       </c>
       <c r="AK30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5889,7 +5956,7 @@
         <v>11</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
@@ -5939,46 +6006,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
         <v>20</v>
       </c>
       <c r="F31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G31" t="n">
-        <v>0.323</v>
+        <v>0.328</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K31" t="n">
         <v>0.43</v>
       </c>
       <c r="L31" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M31" t="n">
         <v>18.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O31" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P31" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.739</v>
+        <v>0.737</v>
       </c>
       <c r="R31" t="n">
         <v>10.7</v>
@@ -5987,7 +6054,7 @@
         <v>32.7</v>
       </c>
       <c r="T31" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U31" t="n">
         <v>21.8</v>
@@ -5996,25 +6063,25 @@
         <v>15.6</v>
       </c>
       <c r="W31" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z31" t="n">
         <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
         <v>91.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD31" t="n">
         <v>25</v>
@@ -6035,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="AJ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
@@ -6050,7 +6117,7 @@
         <v>19</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
         <v>25</v>
@@ -6083,16 +6150,16 @@
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-12-2012-13</t>
+          <t>2013-03-12</t>
         </is>
       </c>
     </row>
